--- a/Result/profitability/1591.xlsx
+++ b/Result/profitability/1591.xlsx
@@ -669,7 +669,7 @@
         <v>1.21</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.2575</v>
+        <v>-0.3950000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>0.9850000000000003</v>
@@ -780,7 +780,7 @@
         <v>0.34</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.135</v>
+        <v>-0.2725000000000001</v>
       </c>
       <c r="N3" t="n">
         <v>3.91875</v>
@@ -899,13 +899,13 @@
         <v>-0.19</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.18375</v>
+        <v>-0.32125</v>
       </c>
       <c r="N4" t="n">
         <v>1.61</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -8586,33 +8586,33 @@
         <v>31.69</v>
       </c>
       <c r="G65" t="n">
-        <v>-4</v>
+        <v>-45</v>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>-2.90%</t>
+          <t>-34.34%</t>
         </is>
       </c>
       <c r="I65" t="n">
         <v>-0</v>
       </c>
       <c r="J65" t="n">
-        <v>-4</v>
+        <v>-46</v>
       </c>
       <c r="K65" t="n">
-        <v>-3</v>
+        <v>-45</v>
       </c>
       <c r="L65" t="n">
-        <v>-0.08</v>
+        <v>-1.18</v>
       </c>
       <c r="M65" t="n">
-        <v>-0.4525</v>
+        <v>-0.5900000000000001</v>
       </c>
       <c r="N65" t="n">
         <v>-0.8937499999999994</v>
       </c>
       <c r="O65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P65" t="n">
         <v>1</v>
@@ -8624,7 +8624,7 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T65" t="n">
         <v>0</v>
@@ -8636,10 +8636,10 @@
         <v>115.1</v>
       </c>
       <c r="W65" t="n">
-        <v>0.5900000000000001</v>
+        <v>-0.5099999999999999</v>
       </c>
       <c r="X65" t="n">
-        <v>-0.8805970149253731</v>
+        <v>0.761194029850746</v>
       </c>
       <c r="Y65" t="n">
         <v>56.82</v>
@@ -8648,10 +8648,10 @@
         <v>-2.261042578591325</v>
       </c>
       <c r="AA65" t="n">
-        <v>0.44</v>
+        <v>-0.6599999999999999</v>
       </c>
       <c r="AB65" t="n">
-        <v>-0.8461538461538461</v>
+        <v>1.269230769230769</v>
       </c>
       <c r="AC65" t="n">
         <v>82.38</v>
@@ -8660,10 +8660,10 @@
         <v>-1.625172617873348</v>
       </c>
       <c r="AE65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>1</v>
@@ -8672,11 +8672,11 @@
         <v>1</v>
       </c>
       <c r="AI65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ65" t="inlineStr">
         <is>
-          <t>EPS成長 / 毛利率成長</t>
+          <t>EPS衰退 / 毛利率成長</t>
         </is>
       </c>
       <c r="AK65" t="n">
